--- a/backend/templates/pr-template 2p.xlsx
+++ b/backend/templates/pr-template 2p.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA680B0-BFC8-4403-88A6-1008B5C9E8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D5AFC4-4A42-47C1-98B2-948614655CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,7 +403,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -508,18 +508,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -532,9 +520,113 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -553,112 +645,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1079,26 +1076,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="61"/>
+      <c r="A2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="74"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1106,439 +1103,439 @@
       </c>
       <c r="B4" s="26"/>
       <c r="C4" s="27"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="68"/>
+      <c r="B5" s="78"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="69" t="s">
+      <c r="E5" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="70"/>
+      <c r="F5" s="80"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="51"/>
-      <c r="B6" s="52"/>
+      <c r="A6" s="83"/>
+      <c r="B6" s="84"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="50"/>
+      <c r="F6" s="82"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E7" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="52" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="54"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="46"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="48"/>
+      <c r="A9" s="42"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="87"/>
       <c r="F9" s="39">
         <f t="shared" ref="F9:F42" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="46"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="48"/>
+      <c r="A10" s="42"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="87"/>
       <c r="F10" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="46"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45"/>
-      <c r="E11" s="48"/>
+      <c r="A11" s="42"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="87"/>
       <c r="F11" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="46"/>
-      <c r="B12" s="47"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="48"/>
+      <c r="A12" s="42"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="87"/>
       <c r="F12" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="46"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="48"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="87"/>
       <c r="F13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="46"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="48"/>
+      <c r="A14" s="42"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="87"/>
       <c r="F14" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="46"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="48"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="43"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="87"/>
       <c r="F15" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="46"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="45"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="48"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="43"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="46"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="48"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="87"/>
       <c r="F17" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="46"/>
-      <c r="B18" s="47"/>
-      <c r="C18" s="45"/>
-      <c r="D18" s="45"/>
-      <c r="E18" s="48"/>
+      <c r="A18" s="42"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="87"/>
       <c r="F18" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="46"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45"/>
-      <c r="E19" s="48"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="87"/>
       <c r="F19" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="46"/>
-      <c r="B20" s="47"/>
-      <c r="C20" s="45"/>
-      <c r="D20" s="45"/>
-      <c r="E20" s="48"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="87"/>
       <c r="F20" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="46"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="48"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="87"/>
       <c r="F21" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="46"/>
-      <c r="B22" s="47"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="45"/>
-      <c r="E22" s="48"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="87"/>
       <c r="F22" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="46"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="45"/>
-      <c r="E23" s="48"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="87"/>
       <c r="F23" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="46"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="45"/>
-      <c r="E24" s="48"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="87"/>
       <c r="F24" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="46"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="48"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="87"/>
       <c r="F25" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="46"/>
-      <c r="B26" s="47"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="48"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="87"/>
       <c r="F26" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="46"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="48"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="87"/>
       <c r="F27" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="46"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="45"/>
-      <c r="D28" s="45"/>
-      <c r="E28" s="48"/>
+      <c r="A28" s="42"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="87"/>
       <c r="F28" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="46"/>
-      <c r="B29" s="47"/>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="48"/>
+      <c r="A29" s="42"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="87"/>
       <c r="F29" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="46"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="48"/>
+      <c r="A30" s="42"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="87"/>
       <c r="F30" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="46"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="48"/>
+      <c r="A31" s="42"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="87"/>
       <c r="F31" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="46"/>
-      <c r="B32" s="47"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="48"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="87"/>
       <c r="F32" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="46"/>
-      <c r="B33" s="47"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="45"/>
-      <c r="E33" s="48"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="87"/>
       <c r="F33" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="46"/>
-      <c r="B34" s="47"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="45"/>
-      <c r="E34" s="48"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="87"/>
       <c r="F34" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="46"/>
-      <c r="B35" s="47"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="45"/>
-      <c r="E35" s="48"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="43"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="87"/>
       <c r="F35" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="46"/>
-      <c r="B36" s="47"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="48"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="43"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="87"/>
       <c r="F36" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="46"/>
-      <c r="B37" s="47"/>
-      <c r="C37" s="45"/>
-      <c r="D37" s="45"/>
-      <c r="E37" s="48"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="43"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="87"/>
       <c r="F37" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="46"/>
-      <c r="B38" s="47"/>
-      <c r="C38" s="45"/>
-      <c r="D38" s="45"/>
-      <c r="E38" s="48"/>
+      <c r="A38" s="42"/>
+      <c r="B38" s="43"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="87"/>
       <c r="F38" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G38" s="91" t="s">
+      <c r="G38" s="44" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="46"/>
-      <c r="B39" s="47"/>
-      <c r="C39" s="45"/>
-      <c r="D39" s="45"/>
-      <c r="E39" s="48"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="43"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="87"/>
       <c r="F39" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G39" s="91" t="s">
+      <c r="G39" s="44" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="46"/>
-      <c r="B40" s="47"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="48"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="43"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="87"/>
       <c r="F40" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="46"/>
-      <c r="B41" s="47"/>
-      <c r="C41" s="45"/>
-      <c r="D41" s="45"/>
-      <c r="E41" s="48"/>
+      <c r="A41" s="42"/>
+      <c r="B41" s="43"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="87"/>
       <c r="F41" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="46"/>
-      <c r="B42" s="47"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="48"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="43"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="87"/>
       <c r="F42" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1549,7 +1546,7 @@
       <c r="B43" s="28"/>
       <c r="C43" s="34"/>
       <c r="D43" s="29"/>
-      <c r="E43" s="42"/>
+      <c r="E43" s="88"/>
       <c r="F43" s="39">
         <f t="shared" ref="F43:F68" si="1">D43*E43</f>
         <v>0</v>
@@ -1560,7 +1557,7 @@
       <c r="B44" s="23"/>
       <c r="C44" s="10"/>
       <c r="D44" s="23"/>
-      <c r="E44" s="43"/>
+      <c r="E44" s="89"/>
       <c r="F44" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1571,7 +1568,7 @@
       <c r="B45" s="23"/>
       <c r="C45" s="10"/>
       <c r="D45" s="30"/>
-      <c r="E45" s="43"/>
+      <c r="E45" s="89"/>
       <c r="F45" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1582,7 +1579,7 @@
       <c r="B46" s="23"/>
       <c r="C46" s="10"/>
       <c r="D46" s="30"/>
-      <c r="E46" s="43"/>
+      <c r="E46" s="89"/>
       <c r="F46" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1593,7 +1590,7 @@
       <c r="B47" s="23"/>
       <c r="C47" s="10"/>
       <c r="D47" s="30"/>
-      <c r="E47" s="43"/>
+      <c r="E47" s="89"/>
       <c r="F47" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1604,7 +1601,7 @@
       <c r="B48" s="23"/>
       <c r="C48" s="10"/>
       <c r="D48" s="30"/>
-      <c r="E48" s="43"/>
+      <c r="E48" s="89"/>
       <c r="F48" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1615,7 +1612,7 @@
       <c r="B49" s="23"/>
       <c r="C49" s="35"/>
       <c r="D49" s="30"/>
-      <c r="E49" s="43"/>
+      <c r="E49" s="89"/>
       <c r="F49" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1626,7 +1623,7 @@
       <c r="B50" s="23"/>
       <c r="C50" s="10"/>
       <c r="D50" s="30"/>
-      <c r="E50" s="43"/>
+      <c r="E50" s="89"/>
       <c r="F50" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1637,7 +1634,7 @@
       <c r="B51" s="23"/>
       <c r="C51" s="10"/>
       <c r="D51" s="30"/>
-      <c r="E51" s="43"/>
+      <c r="E51" s="89"/>
       <c r="F51" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1648,7 +1645,7 @@
       <c r="B52" s="23"/>
       <c r="C52" s="10"/>
       <c r="D52" s="30"/>
-      <c r="E52" s="43"/>
+      <c r="E52" s="89"/>
       <c r="F52" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1659,7 +1656,7 @@
       <c r="B53" s="23"/>
       <c r="C53" s="10"/>
       <c r="D53" s="30"/>
-      <c r="E53" s="40"/>
+      <c r="E53" s="90"/>
       <c r="F53" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1670,7 +1667,7 @@
       <c r="B54" s="32"/>
       <c r="C54" s="31"/>
       <c r="D54" s="32"/>
-      <c r="E54" s="44"/>
+      <c r="E54" s="40"/>
       <c r="F54" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1681,7 +1678,7 @@
       <c r="B55" s="32"/>
       <c r="C55" s="31"/>
       <c r="D55" s="32"/>
-      <c r="E55" s="44"/>
+      <c r="E55" s="40"/>
       <c r="F55" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1692,7 +1689,7 @@
       <c r="B56" s="33"/>
       <c r="C56" s="36"/>
       <c r="D56" s="30"/>
-      <c r="E56" s="41"/>
+      <c r="E56" s="87"/>
       <c r="F56" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1703,7 +1700,7 @@
       <c r="B57" s="25"/>
       <c r="C57" s="10"/>
       <c r="D57" s="30"/>
-      <c r="E57" s="40"/>
+      <c r="E57" s="90"/>
       <c r="F57" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1714,7 +1711,7 @@
       <c r="B58" s="25"/>
       <c r="C58" s="10"/>
       <c r="D58" s="30"/>
-      <c r="E58" s="40"/>
+      <c r="E58" s="90"/>
       <c r="F58" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1725,7 +1722,7 @@
       <c r="B59" s="25"/>
       <c r="C59" s="37"/>
       <c r="D59" s="30"/>
-      <c r="E59" s="40"/>
+      <c r="E59" s="90"/>
       <c r="F59" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1736,7 +1733,7 @@
       <c r="B60" s="25"/>
       <c r="C60" s="10"/>
       <c r="D60" s="30"/>
-      <c r="E60" s="40"/>
+      <c r="E60" s="90"/>
       <c r="F60" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1747,7 +1744,7 @@
       <c r="B61" s="24"/>
       <c r="C61" s="10"/>
       <c r="D61" s="30"/>
-      <c r="E61" s="40"/>
+      <c r="E61" s="90"/>
       <c r="F61" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1758,7 +1755,7 @@
       <c r="B62" s="24"/>
       <c r="C62" s="10"/>
       <c r="D62" s="30"/>
-      <c r="E62" s="40"/>
+      <c r="E62" s="90"/>
       <c r="F62" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1769,7 +1766,7 @@
       <c r="B63" s="24"/>
       <c r="C63" s="10"/>
       <c r="D63" s="30"/>
-      <c r="E63" s="40"/>
+      <c r="E63" s="90"/>
       <c r="F63" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1780,7 +1777,7 @@
       <c r="B64" s="24"/>
       <c r="C64" s="10"/>
       <c r="D64" s="30"/>
-      <c r="E64" s="40"/>
+      <c r="E64" s="90"/>
       <c r="F64" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1791,7 +1788,7 @@
       <c r="B65" s="24"/>
       <c r="C65" s="10"/>
       <c r="D65" s="30"/>
-      <c r="E65" s="40"/>
+      <c r="E65" s="90"/>
       <c r="F65" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1802,7 +1799,7 @@
       <c r="B66" s="11"/>
       <c r="C66" s="37"/>
       <c r="D66" s="30"/>
-      <c r="E66" s="40"/>
+      <c r="E66" s="90"/>
       <c r="F66" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1813,7 +1810,7 @@
       <c r="B67" s="11"/>
       <c r="C67" s="37"/>
       <c r="D67" s="30"/>
-      <c r="E67" s="40"/>
+      <c r="E67" s="90"/>
       <c r="F67" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1824,7 +1821,7 @@
       <c r="B68" s="11"/>
       <c r="C68" s="37"/>
       <c r="D68" s="38"/>
-      <c r="E68" s="40"/>
+      <c r="E68" s="90"/>
       <c r="F68" s="39">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1834,44 +1831,44 @@
       <c r="A69" s="12"/>
       <c r="B69" s="13"/>
       <c r="C69" s="14"/>
-      <c r="D69" s="78" t="s">
+      <c r="D69" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="79"/>
+      <c r="E69" s="55"/>
       <c r="F69" s="9">
         <f>SUM(F9:F68)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88" t="s">
+      <c r="A70" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="89"/>
-      <c r="C70" s="89"/>
-      <c r="D70" s="89"/>
-      <c r="E70" s="89"/>
-      <c r="F70" s="90"/>
+      <c r="B70" s="65"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="65"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="66"/>
     </row>
     <row r="71" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="80"/>
-      <c r="B71" s="81"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="81"/>
-      <c r="E71" s="81"/>
-      <c r="F71" s="82"/>
+      <c r="A71" s="56"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="58"/>
     </row>
     <row r="72" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83" t="s">
+      <c r="A72" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="84"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="86" t="s">
+      <c r="B72" s="60"/>
+      <c r="C72" s="61"/>
+      <c r="D72" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E72" s="86"/>
-      <c r="F72" s="87"/>
+      <c r="E72" s="62"/>
+      <c r="F72" s="63"/>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
@@ -1879,9 +1876,9 @@
       </c>
       <c r="B73" s="15"/>
       <c r="C73" s="21"/>
-      <c r="D73" s="71"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="73"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="46"/>
+      <c r="F73" s="47"/>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
@@ -1889,9 +1886,9 @@
       </c>
       <c r="B74" s="15"/>
       <c r="C74" s="16"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="75"/>
+      <c r="D74" s="48"/>
+      <c r="E74" s="48"/>
+      <c r="F74" s="49"/>
     </row>
     <row r="75" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="17" t="s">
@@ -1899,12 +1896,12 @@
       </c>
       <c r="B75" s="18"/>
       <c r="C75" s="22"/>
-      <c r="D75" s="76" t="s">
+      <c r="D75" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E75" s="76"/>
-      <c r="F75" s="77"/>
-      <c r="G75" s="91" t="s">
+      <c r="E75" s="50"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="44" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1915,7 +1912,7 @@
       <c r="D76" s="19"/>
       <c r="E76" s="19"/>
       <c r="F76" s="20"/>
-      <c r="G76" s="91" t="s">
+      <c r="G76" s="44" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1924,6 +1921,18 @@
     <sortCondition ref="K6:K56"/>
   </sortState>
   <mergeCells count="23">
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="D73:F73"/>
     <mergeCell ref="D74:F74"/>
     <mergeCell ref="D75:F75"/>
@@ -1935,18 +1944,6 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="C70:F70"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="1.7716535433070868" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/pr-template 2p.xlsx
+++ b/backend/templates/pr-template 2p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3D5AFC4-4A42-47C1-98B2-948614655CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A30168E-472D-4764-93A4-C74E407D2E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -424,9 +424,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -483,22 +480,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -517,11 +504,35 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
@@ -645,17 +656,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1076,843 +1078,843 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="68"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="71"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="71"/>
+      <c r="A2" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="74"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74"/>
+      <c r="A3" s="75"/>
+      <c r="B3" s="76"/>
+      <c r="C3" s="76"/>
+      <c r="D3" s="76"/>
+      <c r="E3" s="76"/>
+      <c r="F3" s="77"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="76"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="79"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="78"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="82" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="80"/>
+      <c r="F5" s="83"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="83"/>
-      <c r="B6" s="84"/>
+      <c r="A6" s="86"/>
+      <c r="B6" s="87"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="81" t="s">
+      <c r="E6" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="82"/>
+      <c r="F6" s="85"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="88" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="52" t="s">
+      <c r="B7" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="52" t="s">
+      <c r="C7" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="52" t="s">
+      <c r="D7" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="52" t="s">
+      <c r="E7" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="52" t="s">
+      <c r="F7" s="55" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="86"/>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
+      <c r="A8" s="89"/>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="39">
+      <c r="A9" s="37"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="34">
         <f t="shared" ref="F9:F42" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="42"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="87"/>
-      <c r="F10" s="39">
+      <c r="A10" s="37"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="42"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="39">
+      <c r="A11" s="37"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="87"/>
-      <c r="F12" s="39">
+      <c r="A12" s="37"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="42"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="39">
+      <c r="A13" s="37"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="42"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="39">
+      <c r="A14" s="37"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="87"/>
-      <c r="F15" s="39">
+      <c r="A15" s="37"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="42"/>
-      <c r="B16" s="43"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="87"/>
-      <c r="F16" s="39">
+      <c r="A16" s="37"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="42"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="87"/>
-      <c r="F17" s="39">
+      <c r="A17" s="37"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="39">
+      <c r="A18" s="37"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="42"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="39">
+      <c r="A19" s="37"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="42"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="39">
+      <c r="A20" s="37"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="87"/>
-      <c r="F21" s="39">
+      <c r="A21" s="37"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="90"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="42"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="87"/>
-      <c r="F22" s="39">
+      <c r="A22" s="37"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="90"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="41"/>
-      <c r="E23" s="87"/>
-      <c r="F23" s="39">
+      <c r="A23" s="37"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="42"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="39">
+      <c r="A24" s="37"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="42"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="87"/>
-      <c r="F25" s="39">
+      <c r="A25" s="37"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="36"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="42"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="87"/>
-      <c r="F26" s="39">
+      <c r="A26" s="37"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="90"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="42"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="87"/>
-      <c r="F27" s="39">
+      <c r="A27" s="37"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="87"/>
-      <c r="F28" s="39">
+      <c r="A28" s="37"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="42"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="39">
+      <c r="A29" s="37"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="90"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="42"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="39">
+      <c r="A30" s="37"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="42"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="41"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="39">
+      <c r="A31" s="37"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="90"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="42"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="87"/>
-      <c r="F32" s="39">
+      <c r="A32" s="37"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="90"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="39"/>
+      <c r="F32" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="42"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="87"/>
-      <c r="F33" s="39">
+      <c r="A33" s="37"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="90"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="42"/>
-      <c r="B34" s="43"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="39">
+      <c r="A34" s="37"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="90"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="42"/>
-      <c r="B35" s="43"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="87"/>
-      <c r="F35" s="39">
+      <c r="A35" s="37"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="90"/>
+      <c r="D35" s="36"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="42"/>
-      <c r="B36" s="43"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="87"/>
-      <c r="F36" s="39">
+      <c r="A36" s="37"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="90"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="42"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="87"/>
-      <c r="F37" s="39">
+      <c r="A37" s="37"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="90"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="42"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="41"/>
-      <c r="E38" s="87"/>
-      <c r="F38" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="44" t="s">
+      <c r="A38" s="37"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G38" s="38" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="42"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="44" t="s">
+      <c r="A39" s="37"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="39"/>
+      <c r="F39" s="34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G39" s="38" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="42"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="39">
+      <c r="A40" s="37"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="39"/>
+      <c r="F40" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="42"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="39">
+      <c r="A41" s="37"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="39"/>
+      <c r="F41" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="42"/>
-      <c r="B42" s="43"/>
-      <c r="C42" s="41"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="87"/>
-      <c r="F42" s="39">
+      <c r="A42" s="37"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="36"/>
+      <c r="E42" s="39"/>
+      <c r="F42" s="34">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="8"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="88"/>
-      <c r="F43" s="39">
+      <c r="B43" s="27"/>
+      <c r="C43" s="43"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="34">
         <f t="shared" ref="F43:F68" si="1">D43*E43</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="8"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="89"/>
-      <c r="F44" s="39">
+      <c r="B44" s="22"/>
+      <c r="C44" s="44"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="41"/>
+      <c r="F44" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="8"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="89"/>
-      <c r="F45" s="39">
+      <c r="B45" s="22"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="8"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="39">
+      <c r="B46" s="22"/>
+      <c r="C46" s="44"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="8"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="89"/>
-      <c r="F47" s="39">
+      <c r="B47" s="22"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="8"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="89"/>
-      <c r="F48" s="39">
+      <c r="B48" s="22"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="8"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="35"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="39">
+      <c r="B49" s="22"/>
+      <c r="C49" s="45"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="8"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="89"/>
-      <c r="F50" s="39">
+      <c r="B50" s="22"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="29"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="8"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="89"/>
-      <c r="F51" s="39">
+      <c r="B51" s="22"/>
+      <c r="C51" s="44"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="41"/>
+      <c r="F51" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="8"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="89"/>
-      <c r="F52" s="39">
+      <c r="B52" s="22"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="8"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="90"/>
-      <c r="F53" s="39">
+      <c r="B53" s="22"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="8"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="39">
+      <c r="B54" s="30"/>
+      <c r="C54" s="46"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="8"/>
-      <c r="B55" s="32"/>
-      <c r="C55" s="31"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="39">
+      <c r="B55" s="30"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="8"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="36"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="87"/>
-      <c r="F56" s="39">
+      <c r="B56" s="31"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="29"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="8"/>
-      <c r="B57" s="25"/>
-      <c r="C57" s="10"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="90"/>
-      <c r="F57" s="39">
+      <c r="B57" s="24"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="29"/>
+      <c r="E57" s="42"/>
+      <c r="F57" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="8"/>
-      <c r="B58" s="25"/>
-      <c r="C58" s="10"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="90"/>
-      <c r="F58" s="39">
+      <c r="B58" s="24"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="42"/>
+      <c r="F58" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="8"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="39">
+      <c r="B59" s="24"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="29"/>
+      <c r="E59" s="42"/>
+      <c r="F59" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="8"/>
-      <c r="B60" s="25"/>
-      <c r="C60" s="10"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="39">
+      <c r="B60" s="24"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="29"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="8"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="10"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="90"/>
-      <c r="F61" s="39">
+      <c r="B61" s="23"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="8"/>
-      <c r="B62" s="24"/>
-      <c r="C62" s="10"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="90"/>
-      <c r="F62" s="39">
+      <c r="B62" s="23"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="29"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="8"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="10"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="90"/>
-      <c r="F63" s="39">
+      <c r="B63" s="23"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="8"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="10"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="90"/>
-      <c r="F64" s="39">
+      <c r="B64" s="23"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="8"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="10"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="90"/>
-      <c r="F65" s="39">
+      <c r="B65" s="23"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="29"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="8"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="90"/>
-      <c r="F66" s="39">
+      <c r="B66" s="10"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="8"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="90"/>
-      <c r="F67" s="39">
+      <c r="B67" s="10"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="8"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="90"/>
-      <c r="F68" s="39">
+      <c r="B68" s="10"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="33"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="12"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="54" t="s">
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="13"/>
+      <c r="D69" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="55"/>
+      <c r="E69" s="58"/>
       <c r="F69" s="9">
         <f>SUM(F9:F68)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="64" t="s">
+      <c r="A70" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="65"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="65"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="66"/>
+      <c r="B70" s="68"/>
+      <c r="C70" s="68"/>
+      <c r="D70" s="68"/>
+      <c r="E70" s="68"/>
+      <c r="F70" s="69"/>
     </row>
     <row r="71" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="56"/>
-      <c r="B71" s="57"/>
-      <c r="C71" s="57"/>
-      <c r="D71" s="57"/>
-      <c r="E71" s="57"/>
-      <c r="F71" s="58"/>
+      <c r="A71" s="59"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="61"/>
     </row>
     <row r="72" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="59" t="s">
+      <c r="A72" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="60"/>
-      <c r="C72" s="61"/>
-      <c r="D72" s="62" t="s">
+      <c r="B72" s="63"/>
+      <c r="C72" s="64"/>
+      <c r="D72" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="E72" s="62"/>
-      <c r="F72" s="63"/>
+      <c r="E72" s="65"/>
+      <c r="F72" s="66"/>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B73" s="15"/>
-      <c r="C73" s="21"/>
-      <c r="D73" s="45"/>
-      <c r="E73" s="46"/>
-      <c r="F73" s="47"/>
+      <c r="B73" s="14"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="48"/>
+      <c r="E73" s="49"/>
+      <c r="F73" s="50"/>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B74" s="15"/>
-      <c r="C74" s="16"/>
-      <c r="D74" s="48"/>
-      <c r="E74" s="48"/>
-      <c r="F74" s="49"/>
+      <c r="B74" s="14"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="51"/>
+      <c r="E74" s="51"/>
+      <c r="F74" s="52"/>
     </row>
     <row r="75" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B75" s="18"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="50" t="s">
+      <c r="B75" s="17"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="E75" s="50"/>
-      <c r="F75" s="51"/>
-      <c r="G75" s="44" t="s">
+      <c r="E75" s="53"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="38" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="6"/>
-      <c r="B76" s="19"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="44" t="s">
+      <c r="B76" s="18"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="38" t="s">
         <v>23</v>
       </c>
     </row>

--- a/backend/templates/pr-template 2p.xlsx
+++ b/backend/templates/pr-template 2p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A30168E-472D-4764-93A4-C74E407D2E42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892CEB63-610D-4560-8910-65877A75C193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -534,6 +534,71 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
@@ -555,12 +620,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -598,65 +657,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1071,6 +1071,7 @@
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="6" width="13.54296875" customWidth="1"/>
     <col min="7" max="7" width="5.36328125" customWidth="1"/>
+    <col min="12" max="12" width="35.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -1078,26 +1079,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="71"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="58"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="74"/>
+      <c r="A2" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="61"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="75"/>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
-      <c r="F3" s="77"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1105,38 +1106,38 @@
       </c>
       <c r="B4" s="25"/>
       <c r="C4" s="26"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="79"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="66"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="81"/>
+      <c r="B5" s="68"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="82" t="s">
+      <c r="E5" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="83"/>
+      <c r="F5" s="70"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="86"/>
-      <c r="B6" s="87"/>
+      <c r="A6" s="51"/>
+      <c r="B6" s="52"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="85"/>
+      <c r="F6" s="50"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="88" t="s">
+      <c r="A7" s="53" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="55" t="s">
@@ -1156,7 +1157,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="89"/>
+      <c r="A8" s="54"/>
       <c r="B8" s="56"/>
       <c r="C8" s="56"/>
       <c r="D8" s="56"/>
@@ -1166,7 +1167,7 @@
     <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="37"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="90"/>
+      <c r="C9" s="48"/>
       <c r="D9" s="36"/>
       <c r="E9" s="39"/>
       <c r="F9" s="34">
@@ -1177,7 +1178,7 @@
     <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="37"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="90"/>
+      <c r="C10" s="48"/>
       <c r="D10" s="36"/>
       <c r="E10" s="39"/>
       <c r="F10" s="34">
@@ -1188,7 +1189,7 @@
     <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="37"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="90"/>
+      <c r="C11" s="48"/>
       <c r="D11" s="36"/>
       <c r="E11" s="39"/>
       <c r="F11" s="34">
@@ -1199,7 +1200,7 @@
     <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="37"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="90"/>
+      <c r="C12" s="48"/>
       <c r="D12" s="36"/>
       <c r="E12" s="39"/>
       <c r="F12" s="34">
@@ -1210,7 +1211,7 @@
     <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="37"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="90"/>
+      <c r="C13" s="48"/>
       <c r="D13" s="36"/>
       <c r="E13" s="39"/>
       <c r="F13" s="34">
@@ -1221,7 +1222,7 @@
     <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="37"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="90"/>
+      <c r="C14" s="48"/>
       <c r="D14" s="36"/>
       <c r="E14" s="39"/>
       <c r="F14" s="34">
@@ -1232,7 +1233,7 @@
     <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="37"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="90"/>
+      <c r="C15" s="48"/>
       <c r="D15" s="36"/>
       <c r="E15" s="39"/>
       <c r="F15" s="34">
@@ -1243,7 +1244,7 @@
     <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="37"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="90"/>
+      <c r="C16" s="48"/>
       <c r="D16" s="36"/>
       <c r="E16" s="39"/>
       <c r="F16" s="34">
@@ -1254,7 +1255,7 @@
     <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="37"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="90"/>
+      <c r="C17" s="48"/>
       <c r="D17" s="36"/>
       <c r="E17" s="39"/>
       <c r="F17" s="34">
@@ -1265,7 +1266,7 @@
     <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="37"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="90"/>
+      <c r="C18" s="48"/>
       <c r="D18" s="36"/>
       <c r="E18" s="39"/>
       <c r="F18" s="34">
@@ -1276,7 +1277,7 @@
     <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="37"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="90"/>
+      <c r="C19" s="48"/>
       <c r="D19" s="36"/>
       <c r="E19" s="39"/>
       <c r="F19" s="34">
@@ -1287,7 +1288,7 @@
     <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="37"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="90"/>
+      <c r="C20" s="48"/>
       <c r="D20" s="36"/>
       <c r="E20" s="39"/>
       <c r="F20" s="34">
@@ -1298,7 +1299,7 @@
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="37"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="90"/>
+      <c r="C21" s="48"/>
       <c r="D21" s="36"/>
       <c r="E21" s="39"/>
       <c r="F21" s="34">
@@ -1309,7 +1310,7 @@
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="37"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="90"/>
+      <c r="C22" s="48"/>
       <c r="D22" s="36"/>
       <c r="E22" s="39"/>
       <c r="F22" s="34">
@@ -1320,7 +1321,7 @@
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="37"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="90"/>
+      <c r="C23" s="48"/>
       <c r="D23" s="36"/>
       <c r="E23" s="39"/>
       <c r="F23" s="34">
@@ -1331,7 +1332,7 @@
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="37"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="90"/>
+      <c r="C24" s="48"/>
       <c r="D24" s="36"/>
       <c r="E24" s="39"/>
       <c r="F24" s="34">
@@ -1342,7 +1343,7 @@
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="37"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="90"/>
+      <c r="C25" s="48"/>
       <c r="D25" s="36"/>
       <c r="E25" s="39"/>
       <c r="F25" s="34">
@@ -1353,7 +1354,7 @@
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="37"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="90"/>
+      <c r="C26" s="48"/>
       <c r="D26" s="36"/>
       <c r="E26" s="39"/>
       <c r="F26" s="34">
@@ -1364,7 +1365,7 @@
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="37"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="90"/>
+      <c r="C27" s="48"/>
       <c r="D27" s="36"/>
       <c r="E27" s="39"/>
       <c r="F27" s="34">
@@ -1375,7 +1376,7 @@
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="37"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="90"/>
+      <c r="C28" s="48"/>
       <c r="D28" s="36"/>
       <c r="E28" s="39"/>
       <c r="F28" s="34">
@@ -1386,7 +1387,7 @@
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="37"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="90"/>
+      <c r="C29" s="48"/>
       <c r="D29" s="36"/>
       <c r="E29" s="39"/>
       <c r="F29" s="34">
@@ -1397,7 +1398,7 @@
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="37"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="90"/>
+      <c r="C30" s="48"/>
       <c r="D30" s="36"/>
       <c r="E30" s="39"/>
       <c r="F30" s="34">
@@ -1408,7 +1409,7 @@
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="37"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="90"/>
+      <c r="C31" s="48"/>
       <c r="D31" s="36"/>
       <c r="E31" s="39"/>
       <c r="F31" s="34">
@@ -1419,7 +1420,7 @@
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="37"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="90"/>
+      <c r="C32" s="48"/>
       <c r="D32" s="36"/>
       <c r="E32" s="39"/>
       <c r="F32" s="34">
@@ -1430,7 +1431,7 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="37"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="90"/>
+      <c r="C33" s="48"/>
       <c r="D33" s="36"/>
       <c r="E33" s="39"/>
       <c r="F33" s="34">
@@ -1441,7 +1442,7 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="37"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="90"/>
+      <c r="C34" s="48"/>
       <c r="D34" s="36"/>
       <c r="E34" s="39"/>
       <c r="F34" s="34">
@@ -1452,7 +1453,7 @@
     <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="37"/>
       <c r="B35" s="27"/>
-      <c r="C35" s="90"/>
+      <c r="C35" s="48"/>
       <c r="D35" s="36"/>
       <c r="E35" s="39"/>
       <c r="F35" s="34">
@@ -1463,7 +1464,7 @@
     <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="37"/>
       <c r="B36" s="27"/>
-      <c r="C36" s="90"/>
+      <c r="C36" s="48"/>
       <c r="D36" s="36"/>
       <c r="E36" s="39"/>
       <c r="F36" s="34">
@@ -1474,7 +1475,7 @@
     <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="37"/>
       <c r="B37" s="27"/>
-      <c r="C37" s="90"/>
+      <c r="C37" s="48"/>
       <c r="D37" s="36"/>
       <c r="E37" s="39"/>
       <c r="F37" s="34">
@@ -1485,7 +1486,7 @@
     <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="37"/>
       <c r="B38" s="27"/>
-      <c r="C38" s="90"/>
+      <c r="C38" s="48"/>
       <c r="D38" s="36"/>
       <c r="E38" s="39"/>
       <c r="F38" s="34">
@@ -1499,7 +1500,7 @@
     <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="37"/>
       <c r="B39" s="27"/>
-      <c r="C39" s="90"/>
+      <c r="C39" s="48"/>
       <c r="D39" s="36"/>
       <c r="E39" s="39"/>
       <c r="F39" s="34">
@@ -1513,7 +1514,7 @@
     <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="37"/>
       <c r="B40" s="27"/>
-      <c r="C40" s="90"/>
+      <c r="C40" s="48"/>
       <c r="D40" s="36"/>
       <c r="E40" s="39"/>
       <c r="F40" s="34">
@@ -1524,7 +1525,7 @@
     <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="37"/>
       <c r="B41" s="27"/>
-      <c r="C41" s="90"/>
+      <c r="C41" s="48"/>
       <c r="D41" s="36"/>
       <c r="E41" s="39"/>
       <c r="F41" s="34">
@@ -1535,7 +1536,7 @@
     <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="37"/>
       <c r="B42" s="27"/>
-      <c r="C42" s="90"/>
+      <c r="C42" s="48"/>
       <c r="D42" s="36"/>
       <c r="E42" s="39"/>
       <c r="F42" s="34">
@@ -1833,44 +1834,44 @@
       <c r="A69" s="11"/>
       <c r="B69" s="12"/>
       <c r="C69" s="13"/>
-      <c r="D69" s="57" t="s">
+      <c r="D69" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="58"/>
+      <c r="E69" s="79"/>
       <c r="F69" s="9">
         <f>SUM(F9:F68)</f>
         <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="67" t="s">
+      <c r="A70" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="69"/>
+      <c r="B70" s="89"/>
+      <c r="C70" s="89"/>
+      <c r="D70" s="89"/>
+      <c r="E70" s="89"/>
+      <c r="F70" s="90"/>
     </row>
     <row r="71" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="59"/>
-      <c r="B71" s="60"/>
-      <c r="C71" s="60"/>
-      <c r="D71" s="60"/>
-      <c r="E71" s="60"/>
-      <c r="F71" s="61"/>
+      <c r="A71" s="80"/>
+      <c r="B71" s="81"/>
+      <c r="C71" s="81"/>
+      <c r="D71" s="81"/>
+      <c r="E71" s="81"/>
+      <c r="F71" s="82"/>
     </row>
     <row r="72" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="62" t="s">
+      <c r="A72" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="63"/>
-      <c r="C72" s="64"/>
-      <c r="D72" s="65" t="s">
+      <c r="B72" s="84"/>
+      <c r="C72" s="85"/>
+      <c r="D72" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="E72" s="65"/>
-      <c r="F72" s="66"/>
+      <c r="E72" s="86"/>
+      <c r="F72" s="87"/>
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
@@ -1878,9 +1879,9 @@
       </c>
       <c r="B73" s="14"/>
       <c r="C73" s="20"/>
-      <c r="D73" s="48"/>
-      <c r="E73" s="49"/>
-      <c r="F73" s="50"/>
+      <c r="D73" s="71"/>
+      <c r="E73" s="72"/>
+      <c r="F73" s="73"/>
     </row>
     <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
@@ -1888,9 +1889,9 @@
       </c>
       <c r="B74" s="14"/>
       <c r="C74" s="15"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="52"/>
+      <c r="D74" s="74"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="75"/>
     </row>
     <row r="75" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
@@ -1898,11 +1899,11 @@
       </c>
       <c r="B75" s="17"/>
       <c r="C75" s="21"/>
-      <c r="D75" s="53" t="s">
+      <c r="D75" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="E75" s="53"/>
-      <c r="F75" s="54"/>
+      <c r="E75" s="76"/>
+      <c r="F75" s="77"/>
       <c r="G75" s="38" t="s">
         <v>22</v>
       </c>
@@ -1923,18 +1924,6 @@
     <sortCondition ref="K6:K56"/>
   </sortState>
   <mergeCells count="23">
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
     <mergeCell ref="D73:F73"/>
     <mergeCell ref="D74:F74"/>
     <mergeCell ref="D75:F75"/>
@@ -1946,6 +1935,18 @@
     <mergeCell ref="E7:E8"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="C70:F70"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="1.7716535433070868" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId1"/>

--- a/backend/templates/pr-template 2p.xlsx
+++ b/backend/templates/pr-template 2p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892CEB63-610D-4560-8910-65877A75C193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88E6606-11BF-4DD1-991B-0046F33D188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,7 +125,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,11 +192,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -401,9 +396,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -424,9 +419,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -456,13 +448,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -477,20 +466,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -504,7 +487,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -513,30 +496,134 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -555,109 +642,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1062,7 +1048,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.54296875" customWidth="1"/>
@@ -1079,843 +1065,733 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="58"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="59" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="61"/>
+      <c r="A2" s="69" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="62"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64"/>
+      <c r="A3" s="72"/>
+      <c r="B3" s="73"/>
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="74"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="67" t="s">
+      <c r="A5" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="68"/>
+      <c r="B5" s="78"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="69" t="s">
+      <c r="E5" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="70"/>
+      <c r="F5" s="80"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="51"/>
-      <c r="B6" s="52"/>
+      <c r="A6" s="83"/>
+      <c r="B6" s="84"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="50"/>
+      <c r="F6" s="82"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="85" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="55" t="s">
+      <c r="B7" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="55" t="s">
+      <c r="E7" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="55" t="s">
+      <c r="F7" s="52" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="54"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-    </row>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="37"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="34">
+      <c r="A8" s="86"/>
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="33"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="30">
         <f t="shared" ref="F9:F42" si="0">D9*E9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="37"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="48"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="37"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="48"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="37"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="37"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="37"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="48"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="37"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="37"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="37"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="37"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="37"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="37"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="37"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="37"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="48"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="37"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="37"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="37"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="37"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="37"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="36"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="37"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="37"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="36"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="37"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="36"/>
-      <c r="E30" s="39"/>
-      <c r="F30" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="37"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="37"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="37"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="37"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="37"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="37"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="37"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="37"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G38" s="38" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" s="33"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="33"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" s="33"/>
+      <c r="B12" s="25"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" s="33"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" s="33"/>
+      <c r="B14" s="25"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" s="33"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" s="33"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" s="33"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="33"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="33"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="33"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="33"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="33"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="44"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" s="33"/>
+      <c r="B23" s="25"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" s="33"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" s="33"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="33"/>
+      <c r="B26" s="25"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="33"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="44"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="33"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="44"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="33"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="33"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" s="33"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" s="33"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33" s="33"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34" s="33"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="44"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A35" s="33"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="44"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="33"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="33"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="44"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A38" s="33"/>
+      <c r="B38" s="25"/>
+      <c r="C38" s="44"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="33"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="44"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="33"/>
+      <c r="B40" s="25"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A41" s="33"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="44"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="35"/>
+      <c r="F41" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A42" s="33"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="44"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="8"/>
+      <c r="B43" s="25"/>
+      <c r="C43" s="39"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="30">
+        <f t="shared" ref="F43:F58" si="1">D43*E43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="8"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="8"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G45" s="34" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="37"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G39" s="38" t="s">
+    <row r="46" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="8"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="37"/>
+      <c r="F46" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G46" s="34" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="37"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="36"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="37"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="37"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="8"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="34">
-        <f t="shared" ref="F43:F68" si="1">D43*E43</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="8"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="34">
+    <row r="47" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="8"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="87"/>
+      <c r="F47" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="8"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="34">
+    <row r="48" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="8"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="8"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="34">
+    <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="8"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="8"/>
-      <c r="B47" s="22"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="34">
+    <row r="50" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="8"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="8"/>
-      <c r="B48" s="22"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="34">
+    <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="8"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="8"/>
-      <c r="B49" s="22"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="34">
+    <row r="52" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="8"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="8"/>
-      <c r="B50" s="22"/>
-      <c r="C50" s="44"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="34">
+    <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="8"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="38"/>
+      <c r="F53" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="8"/>
-      <c r="B51" s="22"/>
-      <c r="C51" s="44"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="34">
+    <row r="54" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="8"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="8"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="44"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="34">
+    <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="8"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="42"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="8"/>
-      <c r="B53" s="22"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="34">
+    <row r="56" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="8"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="8"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="46"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="35"/>
-      <c r="F54" s="34">
+    <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="8"/>
+      <c r="B57" s="22"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="38"/>
+      <c r="F57" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="8"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="35"/>
-      <c r="F55" s="34">
+    <row r="58" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="8"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="8"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="47"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="8"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="44"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="8"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="44"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="8"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="8"/>
-      <c r="B60" s="24"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="8"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="44"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="8"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="44"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="42"/>
-      <c r="F62" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="8"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="44"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="42"/>
-      <c r="F63" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="8"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="44"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="8"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="44"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="8"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="42"/>
-      <c r="F66" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="8"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="42"/>
-      <c r="F67" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="8"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="33"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="34">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="78" t="s">
+      <c r="A59" s="10"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="79"/>
-      <c r="F69" s="9">
-        <f>SUM(F9:F68)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="88" t="s">
+      <c r="E59" s="55"/>
+      <c r="F59" s="9">
+        <f>SUM(F9:F58)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="B70" s="89"/>
-      <c r="C70" s="89"/>
-      <c r="D70" s="89"/>
-      <c r="E70" s="89"/>
-      <c r="F70" s="90"/>
-    </row>
-    <row r="71" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A71" s="80"/>
-      <c r="B71" s="81"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="81"/>
-      <c r="E71" s="81"/>
-      <c r="F71" s="82"/>
-    </row>
-    <row r="72" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="83" t="s">
+      <c r="B60" s="65"/>
+      <c r="C60" s="65"/>
+      <c r="D60" s="65"/>
+      <c r="E60" s="65"/>
+      <c r="F60" s="66"/>
+    </row>
+    <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="56"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="58"/>
+    </row>
+    <row r="62" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="84"/>
-      <c r="C72" s="85"/>
-      <c r="D72" s="86" t="s">
+      <c r="B62" s="60"/>
+      <c r="C62" s="61"/>
+      <c r="D62" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E72" s="86"/>
-      <c r="F72" s="87"/>
-    </row>
-    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
+      <c r="E62" s="62"/>
+      <c r="F62" s="63"/>
+    </row>
+    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B73" s="14"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="71"/>
-      <c r="E73" s="72"/>
-      <c r="F73" s="73"/>
-    </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
+      <c r="B63" s="13"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="47"/>
+    </row>
+    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B74" s="14"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="74"/>
-      <c r="E74" s="74"/>
-      <c r="F74" s="75"/>
-    </row>
-    <row r="75" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="16" t="s">
+      <c r="B64" s="13"/>
+      <c r="C64" s="14"/>
+      <c r="D64" s="48"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="49"/>
+    </row>
+    <row r="65" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B75" s="17"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="76" t="s">
+      <c r="B65" s="16"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="E75" s="76"/>
-      <c r="F75" s="77"/>
-      <c r="G75" s="38" t="s">
+      <c r="E65" s="50"/>
+      <c r="F65" s="51"/>
+      <c r="G65" s="34" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76" s="6"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="38" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" s="6"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="34" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1924,32 +1800,32 @@
     <sortCondition ref="K6:K56"/>
   </sortState>
   <mergeCells count="23">
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D69:E69"/>
-    <mergeCell ref="A71:F71"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="C60:F60"/>
   </mergeCells>
-  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="1.7716535433070868" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.70866141732283461" right="0.51181102362204722" top="0.74803149606299213" bottom="1.7716535433070866" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="94" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/backend/templates/pr-template 2p.xlsx
+++ b/backend/templates/pr-template 2p.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\web-opr\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88E6606-11BF-4DD1-991B-0046F33D188E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62214096-2E51-4F37-940B-794F1172F89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,6 +520,71 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="3"/>
     </xf>
@@ -541,12 +606,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -585,65 +644,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1048,7 +1048,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7.54296875" customWidth="1"/>
@@ -1065,26 +1065,26 @@
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="68"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="55"/>
     </row>
     <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="70"/>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="71"/>
+      <c r="A2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="58"/>
     </row>
     <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="72"/>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="74"/>
+      <c r="A3" s="59"/>
+      <c r="B3" s="60"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="60"/>
+      <c r="E3" s="60"/>
+      <c r="F3" s="61"/>
     </row>
     <row r="4" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
@@ -1092,38 +1092,38 @@
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="76"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="63"/>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="78"/>
+      <c r="B5" s="65"/>
       <c r="C5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="79" t="s">
+      <c r="E5" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="80"/>
+      <c r="F5" s="67"/>
     </row>
     <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="83"/>
-      <c r="B6" s="84"/>
+      <c r="A6" s="48"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="81" t="s">
+      <c r="E6" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="82"/>
+      <c r="F6" s="47"/>
     </row>
     <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="50" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="52" t="s">
@@ -1143,7 +1143,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="86"/>
+      <c r="A8" s="51"/>
       <c r="B8" s="53"/>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
@@ -1531,7 +1531,7 @@
       <c r="D43" s="26"/>
       <c r="E43" s="36"/>
       <c r="F43" s="30">
-        <f t="shared" ref="F43:F58" si="1">D43*E43</f>
+        <f t="shared" ref="F43:F68" si="1">D43*E43</f>
         <v>0</v>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       <c r="B47" s="21"/>
       <c r="C47" s="40"/>
       <c r="D47" s="21"/>
-      <c r="E47" s="87"/>
+      <c r="E47" s="45"/>
       <c r="F47" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1599,7 +1599,7 @@
     <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="8"/>
       <c r="B49" s="21"/>
-      <c r="C49" s="41"/>
+      <c r="C49" s="40"/>
       <c r="D49" s="27"/>
       <c r="E49" s="37"/>
       <c r="F49" s="30">
@@ -1645,7 +1645,7 @@
       <c r="B53" s="21"/>
       <c r="C53" s="40"/>
       <c r="D53" s="27"/>
-      <c r="E53" s="38"/>
+      <c r="E53" s="37"/>
       <c r="F53" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1653,10 +1653,10 @@
     </row>
     <row r="54" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="8"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="31"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="55" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="8"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="31"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="37"/>
       <c r="F55" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="56" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="8"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="43"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="40"/>
       <c r="D56" s="27"/>
-      <c r="E56" s="35"/>
+      <c r="E56" s="37"/>
       <c r="F56" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="57" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="8"/>
-      <c r="B57" s="22"/>
+      <c r="B57" s="21"/>
       <c r="C57" s="40"/>
       <c r="D57" s="27"/>
-      <c r="E57" s="38"/>
+      <c r="E57" s="37"/>
       <c r="F57" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1697,132 +1697,242 @@
     </row>
     <row r="58" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="8"/>
-      <c r="B58" s="22"/>
+      <c r="B58" s="21"/>
       <c r="C58" s="40"/>
       <c r="D58" s="27"/>
-      <c r="E58" s="38"/>
+      <c r="E58" s="37"/>
       <c r="F58" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="10"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="54" t="s">
+    <row r="59" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="8"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="8"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="37"/>
+      <c r="F60" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A61" s="8"/>
+      <c r="B61" s="21"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A62" s="8"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="8"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="38"/>
+      <c r="F63" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A64" s="8"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="8"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="28"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="8"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="43"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="35"/>
+      <c r="F66" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="8"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="40"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="38"/>
+      <c r="F67" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A68" s="8"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="30">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="10"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="55"/>
-      <c r="F59" s="9">
-        <f>SUM(F9:F58)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="64" t="s">
+      <c r="E69" s="76"/>
+      <c r="F69" s="9">
+        <f>SUM(F9:F68)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="65"/>
-      <c r="C60" s="65"/>
-      <c r="D60" s="65"/>
-      <c r="E60" s="65"/>
-      <c r="F60" s="66"/>
-    </row>
-    <row r="61" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A61" s="56"/>
-      <c r="B61" s="57"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="57"/>
-      <c r="E61" s="57"/>
-      <c r="F61" s="58"/>
-    </row>
-    <row r="62" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="59" t="s">
+      <c r="B70" s="86"/>
+      <c r="C70" s="86"/>
+      <c r="D70" s="86"/>
+      <c r="E70" s="86"/>
+      <c r="F70" s="87"/>
+    </row>
+    <row r="71" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="77"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="78"/>
+      <c r="E71" s="78"/>
+      <c r="F71" s="79"/>
+    </row>
+    <row r="72" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="B62" s="60"/>
-      <c r="C62" s="61"/>
-      <c r="D62" s="62" t="s">
+      <c r="B72" s="81"/>
+      <c r="C72" s="82"/>
+      <c r="D72" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="E62" s="62"/>
-      <c r="F62" s="63"/>
-    </row>
-    <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
+      <c r="E72" s="83"/>
+      <c r="F72" s="84"/>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B63" s="13"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="46"/>
-      <c r="F63" s="47"/>
-    </row>
-    <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
+      <c r="B73" s="13"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="68"/>
+      <c r="E73" s="69"/>
+      <c r="F73" s="70"/>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B64" s="13"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="48"/>
-      <c r="E64" s="48"/>
-      <c r="F64" s="49"/>
-    </row>
-    <row r="65" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="15" t="s">
+      <c r="B74" s="13"/>
+      <c r="C74" s="14"/>
+      <c r="D74" s="71"/>
+      <c r="E74" s="71"/>
+      <c r="F74" s="72"/>
+    </row>
+    <row r="75" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B65" s="16"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="50" t="s">
+      <c r="B75" s="16"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="73" t="s">
         <v>15</v>
       </c>
-      <c r="E65" s="50"/>
-      <c r="F65" s="51"/>
-      <c r="G65" s="34" t="s">
+      <c r="E75" s="73"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="34" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="6"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="17"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="34" t="s">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" s="6"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="34" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:K56">
-    <sortCondition ref="K6:K56"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K6:K66">
+    <sortCondition ref="K6:K66"/>
   </sortState>
   <mergeCells count="23">
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D69:E69"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="C70:F70"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:A8"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="C7:C8"/>
     <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:F60"/>
   </mergeCells>
   <pageMargins left="0.70866141732283461" right="0.51181102362204722" top="0.74803149606299213" bottom="1.7716535433070866" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="94" fitToHeight="0" orientation="portrait" r:id="rId1"/>
